--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84D46E96-4AC8-460D-A205-C7A1087DCFBA}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0EEFBB8-034B-49D8-A8F1-AA144358E2F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>need to focus on time management</t>
+  </si>
+  <si>
+    <t>self grooming</t>
+  </si>
+  <si>
+    <t>well prepared for my ca</t>
+  </si>
+  <si>
+    <t>spend quality time with friends</t>
   </si>
 </sst>
 </file>
@@ -1869,114 +1878,230 @@
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="14">
+        <v>400</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>100</v>
+      </c>
+      <c r="E24" s="14">
+        <v>80</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>300</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>310</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>450</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>80</v>
+      </c>
+      <c r="E26" s="14">
+        <v>100</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>400</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>100</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>200</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>380</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>130</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>350</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0EEFBB8-034B-49D8-A8F1-AA144358E2F9}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2C0190-8AC5-4EB4-BEEC-8D49B8CBFC05}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>spend quality time with friends</t>
+  </si>
+  <si>
+    <t>tired</t>
   </si>
 </sst>
 </file>
@@ -2104,48 +2107,96 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>400</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+      <c r="A30" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>150</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>300</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:I44" si="2">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>1150</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" ref="J30:J44" si="3">IF(I30="","",1440-I30)</f>
+        <v>290</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
@@ -2157,11 +2208,11 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K31" s="16"/>
@@ -2179,11 +2230,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K32" s="16"/>
@@ -2201,11 +2252,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K33" s="16"/>
@@ -2223,11 +2274,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K34" s="16"/>
@@ -2245,11 +2296,11 @@
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K35" s="16"/>
@@ -2267,11 +2318,11 @@
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K36" s="16"/>
@@ -2289,11 +2340,11 @@
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K37" s="16"/>
@@ -2311,11 +2362,11 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K38" s="16"/>
@@ -2333,11 +2384,11 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K39" s="16"/>
@@ -2355,11 +2406,11 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K40" s="16"/>
@@ -2377,11 +2428,11 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K41" s="16"/>
@@ -2399,11 +2450,11 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K42" s="16"/>
@@ -2421,11 +2472,11 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K43" s="16"/>
@@ -2443,11 +2494,11 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K44" s="16"/>
@@ -3015,11 +3066,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3037,11 +3088,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3059,11 +3110,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3081,11 +3132,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3103,11 +3154,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3125,11 +3176,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3147,11 +3198,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3169,11 +3220,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3191,11 +3242,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3213,11 +3264,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3235,11 +3286,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3257,11 +3308,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3279,11 +3330,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3301,11 +3352,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3323,11 +3374,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3345,11 +3396,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3367,11 +3418,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3389,11 +3440,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3411,11 +3462,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3433,11 +3484,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3455,11 +3506,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3477,11 +3528,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3499,11 +3550,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3521,11 +3572,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3543,11 +3594,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3565,11 +3616,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3587,11 +3638,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3609,11 +3660,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3631,11 +3682,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3653,11 +3704,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3675,11 +3726,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3697,11 +3748,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3719,11 +3770,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3741,11 +3792,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3763,11 +3814,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3785,11 +3836,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3807,11 +3858,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3829,11 +3880,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3851,11 +3902,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3873,11 +3924,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3895,11 +3946,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3917,11 +3968,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3939,11 +3990,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3961,11 +4012,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3983,11 +4034,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4005,11 +4056,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4027,11 +4078,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4049,11 +4100,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4071,11 +4122,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4093,11 +4144,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4115,11 +4166,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4137,11 +4188,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4159,11 +4210,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4181,11 +4232,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4203,11 +4254,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4225,11 +4276,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4247,11 +4298,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4269,11 +4320,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4291,11 +4342,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4313,11 +4364,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4335,11 +4386,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4357,11 +4408,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4379,11 +4430,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4401,11 +4452,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4423,11 +4474,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4445,11 +4496,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4467,11 +4518,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4489,11 +4540,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4511,11 +4562,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4533,11 +4584,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4555,11 +4606,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4577,11 +4628,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4599,11 +4650,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4621,11 +4672,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4643,11 +4694,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4665,11 +4716,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4687,11 +4738,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4709,11 +4760,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4731,11 +4782,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4753,11 +4804,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4775,11 +4826,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4797,11 +4848,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4819,11 +4870,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4841,11 +4892,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4863,11 +4914,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4885,11 +4936,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4907,11 +4958,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4929,11 +4980,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4951,11 +5002,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4973,11 +5024,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4995,11 +5046,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5017,11 +5068,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5039,11 +5090,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5061,11 +5112,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5083,11 +5134,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5105,11 +5156,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5127,11 +5178,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5149,11 +5200,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5171,11 +5222,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5193,11 +5244,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5215,11 +5266,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5237,11 +5288,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5259,11 +5310,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5281,11 +5332,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5303,11 +5354,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5325,11 +5376,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5347,11 +5398,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5369,11 +5420,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5391,11 +5442,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5413,11 +5464,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5435,11 +5486,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5457,11 +5508,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5479,11 +5530,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5501,11 +5552,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5523,11 +5574,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5545,11 +5596,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5567,11 +5618,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5589,11 +5640,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5611,11 +5662,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5633,11 +5684,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5655,11 +5706,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5677,11 +5728,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5699,11 +5750,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5721,11 +5772,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5743,11 +5794,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5765,11 +5816,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5787,11 +5838,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5809,11 +5860,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5831,11 +5882,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5853,11 +5904,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5875,11 +5926,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5897,11 +5948,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5919,11 +5970,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5941,11 +5992,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5963,11 +6014,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5985,11 +6036,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6007,11 +6058,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6029,11 +6080,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6051,11 +6102,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6073,11 +6124,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6095,11 +6146,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6117,11 +6168,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6139,11 +6190,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6161,11 +6212,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6183,11 +6234,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6205,11 +6256,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6227,11 +6278,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6249,11 +6300,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6271,11 +6322,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6293,11 +6344,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6315,11 +6366,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6337,11 +6388,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6359,11 +6410,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6381,11 +6432,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6403,11 +6454,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6425,11 +6476,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6447,11 +6498,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6469,11 +6520,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6491,11 +6542,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6513,11 +6564,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6535,11 +6586,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6557,11 +6608,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6579,11 +6630,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6601,11 +6652,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6623,11 +6674,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6645,11 +6696,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6667,11 +6718,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6689,11 +6740,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6711,11 +6762,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6733,11 +6784,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6755,11 +6806,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6777,11 +6828,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6799,11 +6850,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6821,11 +6872,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6843,11 +6894,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6865,11 +6916,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6887,11 +6938,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6909,11 +6960,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6931,11 +6982,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6953,11 +7004,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6975,11 +7026,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6997,11 +7048,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7019,11 +7070,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7041,11 +7092,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7063,11 +7114,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7085,11 +7136,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7107,11 +7158,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7129,11 +7180,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7151,11 +7202,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7173,11 +7224,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7195,11 +7246,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7217,11 +7268,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7239,11 +7290,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7261,11 +7312,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7283,11 +7334,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7305,11 +7356,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7327,11 +7378,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7349,11 +7400,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7371,11 +7422,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7393,11 +7444,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7415,11 +7466,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7437,11 +7488,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7459,11 +7510,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7481,11 +7532,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7503,11 +7554,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7525,11 +7576,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7547,11 +7598,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7569,11 +7620,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7591,11 +7642,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7613,11 +7664,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7635,11 +7686,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7657,11 +7708,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7679,11 +7730,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7701,11 +7752,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7723,11 +7774,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7745,11 +7796,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7767,11 +7818,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7789,11 +7840,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7811,11 +7862,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7833,11 +7884,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7855,11 +7906,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7877,11 +7928,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7899,11 +7950,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7921,11 +7972,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7943,11 +7994,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7965,11 +8016,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7987,11 +8038,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8009,11 +8060,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8031,11 +8082,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8053,11 +8104,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8075,11 +8126,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8097,11 +8148,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8119,11 +8170,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8141,11 +8192,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8163,11 +8214,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8185,11 +8236,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8207,11 +8258,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8229,11 +8280,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8251,11 +8302,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8273,11 +8324,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8295,11 +8346,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8317,11 +8368,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8339,11 +8390,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8361,11 +8412,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8383,11 +8434,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8405,11 +8456,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8427,11 +8478,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8449,11 +8500,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8471,11 +8522,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8493,11 +8544,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8515,11 +8566,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8537,11 +8588,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8559,11 +8610,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8581,11 +8632,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8603,11 +8654,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8625,11 +8676,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8647,11 +8698,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8669,11 +8720,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8691,11 +8742,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8713,11 +8764,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8735,11 +8786,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8757,11 +8808,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8779,11 +8830,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8801,11 +8852,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8823,11 +8874,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8845,11 +8896,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8867,11 +8918,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8889,11 +8940,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8911,11 +8962,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8933,11 +8984,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8955,11 +9006,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8977,11 +9028,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8999,11 +9050,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9021,11 +9072,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9043,11 +9094,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9065,11 +9116,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9087,11 +9138,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9109,11 +9160,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9131,11 +9182,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9153,11 +9204,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9175,11 +9226,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9197,11 +9248,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9219,11 +9270,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9241,11 +9292,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9263,11 +9314,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9285,11 +9336,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9307,11 +9358,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9329,11 +9380,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9351,11 +9402,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9373,11 +9424,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9395,11 +9446,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9417,11 +9468,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9439,11 +9490,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9461,11 +9512,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9483,11 +9534,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9505,11 +9556,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9527,11 +9578,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9549,11 +9600,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9571,11 +9622,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9593,11 +9644,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9615,11 +9666,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9637,11 +9688,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9659,11 +9710,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9681,11 +9732,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9703,11 +9754,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9725,11 +9776,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9747,11 +9798,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9769,11 +9820,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9791,11 +9842,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9813,11 +9864,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9835,11 +9886,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9857,11 +9908,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9879,11 +9930,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9901,11 +9952,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9923,11 +9974,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9945,11 +9996,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9967,11 +10018,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9989,11 +10040,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10011,11 +10062,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10033,11 +10084,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10055,11 +10106,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10077,11 +10128,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10099,11 +10150,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10121,11 +10172,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10143,11 +10194,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10165,11 +10216,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10187,11 +10238,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10209,11 +10260,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10231,11 +10282,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10253,11 +10304,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10275,11 +10326,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10297,11 +10348,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB2C0190-8AC5-4EB4-BEEC-8D49B8CBFC05}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0396D527-0DB4-4CF2-BAB1-FF5EA8690A0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>tired</t>
+  </si>
+  <si>
+    <t>need more practice in analytics</t>
   </si>
 </sst>
 </file>
@@ -2199,26 +2202,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>360</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>200</v>
+      </c>
+      <c r="E31" s="14">
+        <v>40</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>400</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0396D527-0DB4-4CF2-BAB1-FF5EA8690A0B}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C946F3-A403-4ECF-8BB7-2225A8C1766B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>need more practice in analytics</t>
+  </si>
+  <si>
+    <t>need time management</t>
   </si>
 </sst>
 </file>
@@ -2209,7 +2212,7 @@
         <v>360</v>
       </c>
       <c r="C31" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="14">
         <v>200</v>
@@ -2228,11 +2231,11 @@
       </c>
       <c r="I31" s="15">
         <f t="shared" si="2"/>
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="3"/>
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>56</v>
@@ -2248,73 +2251,141 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>450</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14">
+        <v>50</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>350</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="14">
+        <v>360</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>50</v>
+      </c>
+      <c r="E33" s="14">
+        <v>160</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>280</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>340</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>80</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="8"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C946F3-A403-4ECF-8BB7-2225A8C1766B}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999A4BB4-AFF0-466D-A312-AA8D550D2B39}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>need time management</t>
+  </si>
+  <si>
+    <t>need on focus on analytical skills</t>
   </si>
 </sst>
 </file>
@@ -2385,73 +2388,141 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>180</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>290</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="14">
+        <v>450</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>210</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>315</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>265</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="14">
+        <v>350</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>220</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>300</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="8"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999A4BB4-AFF0-466D-A312-AA8D550D2B39}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F0EDB04-8FED-4A23-9AB6-651DC6467730}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>need on focus on analytical skills</t>
+  </si>
+  <si>
+    <t>analytics CA went well</t>
   </si>
 </sst>
 </file>
@@ -2522,69 +2525,137 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="14">
+        <v>410</v>
+      </c>
+      <c r="C38" s="14">
+        <v>20</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>400</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>50</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>350</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="14">
+        <v>380</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>180</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>200</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>315</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>365</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F0EDB04-8FED-4A23-9AB6-651DC6467730}"/>
+  <xr:revisionPtr revIDLastSave="462" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5916DC3E-8C0F-4D0B-81BB-12763B5014E1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>analytics CA went well</t>
+  </si>
+  <si>
+    <t>friends birthday</t>
   </si>
 </sst>
 </file>
@@ -944,10 +947,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
@@ -1074,19 +1077,19 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="C6" s="9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E6" s="9">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F6" s="9">
         <v>350</v>
@@ -1095,107 +1098,105 @@
         <v>7</v>
       </c>
       <c r="H6" s="9">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>1090</v>
+        <f t="shared" ref="I6:I70" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1260</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>350</v>
+        <f t="shared" ref="J6:J70" si="1">IF(I6="","",1440-I6)</f>
+        <v>180</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46253</v>
-      </c>
-      <c r="B7" s="14">
-        <v>400</v>
-      </c>
-      <c r="C7" s="14">
-        <v>0</v>
-      </c>
-      <c r="D7" s="14">
-        <v>100</v>
-      </c>
-      <c r="E7" s="14">
-        <v>80</v>
-      </c>
-      <c r="F7" s="14">
-        <v>300</v>
-      </c>
-      <c r="G7" s="14">
-        <v>6</v>
-      </c>
-      <c r="H7" s="14">
-        <v>250</v>
+        <v>46252</v>
+      </c>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9">
+        <v>350</v>
+      </c>
+      <c r="G7" s="9">
+        <v>7</v>
+      </c>
+      <c r="H7" s="9">
+        <v>150</v>
       </c>
       <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1090</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v>310</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>59</v>
+        <v>350</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B8" s="14">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C8" s="14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D8" s="14">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E8" s="14">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F8" s="14">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G8" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>985</v>
+        <v>1130</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v>455</v>
+        <v>310</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>56</v>
@@ -1204,117 +1205,119 @@
         <v>52</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B9" s="14">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="C9" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D9" s="14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E9" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F9" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G9" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="14">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>985</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>60</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B10" s="14">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C10" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D10" s="14">
         <v>100</v>
       </c>
       <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
         <v>200</v>
       </c>
-      <c r="F10" s="14">
-        <v>0</v>
-      </c>
       <c r="G10" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="14">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="14">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11" s="14">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1323,105 +1326,105 @@
         <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1070</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>65</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="14">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C12" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D12" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E12" s="14">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F12" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1140</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="17"/>
+        <v>54</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E13" s="14">
         <v>100</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H13" s="14">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1220</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>56</v>
@@ -1430,27 +1433,25 @@
         <v>63</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>66</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="C14" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D14" s="14">
         <v>80</v>
       </c>
       <c r="E14" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="14">
         <v>350</v>
@@ -1459,130 +1460,130 @@
         <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1150</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>54</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="14">
-        <v>380</v>
+        <v>460</v>
       </c>
       <c r="C15" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D15" s="14">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E15" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H15" s="14">
-        <v>340</v>
+        <v>190</v>
       </c>
       <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v>1150</v>
+        <v>1110</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v>290</v>
+        <v>330</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="C16" s="14">
         <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E16" s="14">
         <v>60</v>
       </c>
       <c r="F16" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1150</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
         <v>60</v>
@@ -1591,39 +1592,41 @@
         <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1110</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>330</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="17"/>
+        <v>54</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C18" s="14">
         <v>30</v>
@@ -1632,7 +1635,7 @@
         <v>60</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F18" s="14">
         <v>0</v>
@@ -1641,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="I18" s="10">
         <f t="shared" si="0"/>
@@ -1652,122 +1655,120 @@
         <v>490</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>71</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
         <v>0</v>
       </c>
-      <c r="D19" s="14">
-        <v>80</v>
-      </c>
-      <c r="E19" s="14">
-        <v>60</v>
-      </c>
       <c r="F19" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>950</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>490</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="14">
-        <v>350</v>
+        <v>480</v>
       </c>
       <c r="C20" s="14">
         <v>0</v>
       </c>
       <c r="D20" s="14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E20" s="14">
         <v>60</v>
       </c>
       <c r="F20" s="14">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="C21" s="14">
         <v>0</v>
       </c>
       <c r="D21" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E21" s="14">
         <v>60</v>
@@ -1779,134 +1780,136 @@
         <v>7</v>
       </c>
       <c r="H21" s="14">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1130</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="14">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C22" s="14">
         <v>0</v>
       </c>
       <c r="D22" s="14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E22" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F22" s="14">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1200</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>240</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
       </c>
       <c r="D23" s="14">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E23" s="14">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F23" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1040</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N23" s="17"/>
+      <c r="N23" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="C24" s="14">
         <v>0</v>
       </c>
       <c r="D24" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E24" s="14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F24" s="14">
         <v>250</v>
@@ -1915,59 +1918,59 @@
         <v>5</v>
       </c>
       <c r="H24" s="14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1140</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>63</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="14">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C25" s="14">
         <v>0</v>
       </c>
       <c r="D25" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E25" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F25" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G25" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1130</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>310</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>52</v>
@@ -1976,15 +1979,13 @@
         <v>63</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>76</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="14">
         <v>450</v>
@@ -1993,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
         <v>0</v>
@@ -2005,702 +2006,750 @@
         <v>0</v>
       </c>
       <c r="H26" s="14">
+        <v>450</v>
+      </c>
+      <c r="I26" s="10">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>80</v>
+      </c>
+      <c r="E27" s="14">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
         <v>400</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K27" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="L27" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M27" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N27" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
         <v>46273</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B28" s="14">
         <v>420</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C28" s="14">
         <v>0</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D28" s="14">
         <v>100</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E28" s="14">
         <v>60</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F28" s="14">
         <v>200</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H28" s="14">
         <v>300</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="L28" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M28" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+      <c r="N28" s="17"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
         <v>46274</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B29" s="14">
         <v>380</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C29" s="14">
         <v>0</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D29" s="14">
         <v>130</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E29" s="14">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F29" s="14">
         <v>350</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G29" s="14">
         <v>7</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H29" s="14">
         <v>350</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K29" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L28" s="16" t="s">
+      <c r="L29" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M28" s="16" t="s">
+      <c r="M29" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N29" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
         <v>46275</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B30" s="14">
         <v>360</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C30" s="14">
         <v>0</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D30" s="14">
         <v>60</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E30" s="14">
         <v>60</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F30" s="14">
         <v>200</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G30" s="14">
         <v>4</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H30" s="14">
         <v>400</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K30" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L30" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M30" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N30" s="17" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B30" s="14">
-        <v>420</v>
-      </c>
-      <c r="C30" s="14">
-        <v>0</v>
-      </c>
-      <c r="D30" s="14">
-        <v>150</v>
-      </c>
-      <c r="E30" s="14">
-        <v>30</v>
-      </c>
-      <c r="F30" s="14">
-        <v>250</v>
-      </c>
-      <c r="G30" s="14">
-        <v>5</v>
-      </c>
-      <c r="H30" s="14">
-        <v>300</v>
-      </c>
-      <c r="I30" s="15">
-        <f t="shared" ref="I30:I44" si="2">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v>1150</v>
-      </c>
-      <c r="J30" s="15">
-        <f t="shared" ref="J30:J44" si="3">IF(I30="","",1440-I30)</f>
-        <v>290</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>150</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>300</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" ref="I31:I45" si="2">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <v>1150</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" ref="J31:J45" si="3">IF(I31="","",1440-I31)</f>
+        <v>290</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
         <v>46277</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B32" s="14">
         <v>360</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C32" s="14">
         <v>30</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D32" s="14">
         <v>200</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E32" s="14">
         <v>40</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F32" s="14">
         <v>0</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G32" s="14">
         <v>0</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H32" s="14">
         <v>400</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I32" s="15">
         <f t="shared" si="2"/>
         <v>1030</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J32" s="15">
         <f t="shared" si="3"/>
         <v>410</v>
       </c>
-      <c r="K31" s="16" t="s">
+      <c r="K32" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="16" t="s">
+      <c r="L32" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M31" s="16" t="s">
+      <c r="M32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N31" s="17" t="s">
+      <c r="N32" s="17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
         <v>46278</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B33" s="14">
         <v>450</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C33" s="14">
         <v>30</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D33" s="14">
         <v>180</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E33" s="14">
         <v>50</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F33" s="14">
         <v>0</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G33" s="14">
         <v>0</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H33" s="14">
         <v>350</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I33" s="15">
         <f t="shared" si="2"/>
         <v>1060</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J33" s="15">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="K33" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L32" s="16" t="s">
+      <c r="L33" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M33" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N32" s="17" t="s">
+      <c r="N33" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
         <v>46279</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B34" s="14">
         <v>360</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C34" s="14">
         <v>0</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D34" s="14">
         <v>50</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E34" s="14">
         <v>160</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F34" s="14">
         <v>200</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G34" s="14">
         <v>4</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H34" s="14">
         <v>280</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I34" s="15">
         <f t="shared" si="2"/>
         <v>1050</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J34" s="15">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K34" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L33" s="16" t="s">
+      <c r="L34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="M34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
+      <c r="N34" s="17"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
         <v>46280</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B35" s="14">
         <v>340</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C35" s="14">
         <v>0</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D35" s="14">
         <v>80</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E35" s="14">
         <v>30</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F35" s="14">
         <v>350</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G35" s="14">
         <v>7</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H35" s="14">
         <v>300</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I35" s="15">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J35" s="15">
         <f t="shared" si="3"/>
         <v>340</v>
       </c>
-      <c r="K34" s="16" t="s">
+      <c r="K35" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L34" s="16" t="s">
+      <c r="L35" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M34" s="16" t="s">
+      <c r="M35" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+      <c r="N35" s="17"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
         <v>46281</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B36" s="14">
         <v>400</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C36" s="14">
         <v>0</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D36" s="14">
         <v>180</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E36" s="14">
         <v>0</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F36" s="14">
         <v>350</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G36" s="14">
         <v>7</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H36" s="14">
         <v>290</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I36" s="15">
         <f t="shared" si="2"/>
         <v>1220</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J36" s="15">
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
-      <c r="K35" s="16" t="s">
+      <c r="K36" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="L35" s="16" t="s">
+      <c r="L36" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="M36" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N35" s="17" t="s">
+      <c r="N36" s="17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
         <v>46282</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B37" s="14">
         <v>450</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C37" s="14">
         <v>0</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D37" s="14">
         <v>210</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E37" s="14">
         <v>0</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F37" s="14">
         <v>200</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G37" s="14">
         <v>4</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H37" s="14">
         <v>315</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I37" s="15">
         <f t="shared" si="2"/>
         <v>1175</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J37" s="15">
         <f t="shared" si="3"/>
         <v>265</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K37" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L36" s="16" t="s">
+      <c r="L37" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M37" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8">
+      <c r="N37" s="17"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
         <v>46283</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B38" s="14">
         <v>350</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C38" s="14">
         <v>0</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D38" s="14">
         <v>220</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E38" s="14">
         <v>0</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F38" s="14">
         <v>250</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G38" s="14">
         <v>5</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H38" s="14">
         <v>300</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I38" s="15">
         <f t="shared" si="2"/>
         <v>1120</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J38" s="15">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
-      <c r="K37" s="16" t="s">
+      <c r="K38" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L37" s="16" t="s">
+      <c r="L38" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M38" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8">
+      <c r="N38" s="17"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
         <v>46284</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B39" s="14">
         <v>410</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C39" s="14">
         <v>20</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D39" s="14">
         <v>120</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E39" s="14">
         <v>60</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F39" s="14">
         <v>0</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G39" s="14">
         <v>0</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H39" s="14">
         <v>400</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I39" s="15">
         <f t="shared" si="2"/>
         <v>1010</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J39" s="15">
         <f t="shared" si="3"/>
         <v>430</v>
       </c>
-      <c r="K38" s="16" t="s">
+      <c r="K39" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L38" s="16" t="s">
+      <c r="L39" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M39" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N38" s="17" t="s">
+      <c r="N39" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
         <v>46285</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B40" s="14">
         <v>400</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C40" s="14">
         <v>20</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D40" s="14">
         <v>200</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E40" s="14">
         <v>50</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F40" s="14">
         <v>0</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G40" s="14">
         <v>0</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H40" s="14">
         <v>350</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I40" s="15">
         <f t="shared" si="2"/>
         <v>1020</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J40" s="15">
         <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="K39" s="16" t="s">
+      <c r="K40" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L39" s="16" t="s">
+      <c r="L40" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8">
+      <c r="N40" s="17"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
         <v>46286</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B41" s="14">
         <v>380</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C41" s="14">
         <v>0</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D41" s="14">
         <v>180</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E41" s="14">
         <v>0</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F41" s="14">
         <v>200</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G41" s="14">
         <v>0</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H41" s="14">
         <v>315</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I41" s="15">
         <f t="shared" si="2"/>
         <v>1075</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J41" s="15">
         <f t="shared" si="3"/>
         <v>365</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="K41" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L40" s="16" t="s">
+      <c r="L41" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M41" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="N41" s="17"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="14">
+        <v>360</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>160</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>290</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
@@ -2756,11 +2805,11 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K45" s="16"/>
@@ -3306,11 +3355,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3328,11 +3377,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I71:I134" si="4">IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J71:J134" si="5">IF(I71="","",1440-I71)</f>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -4714,11 +4763,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4736,11 +4785,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I135:I198" si="6">IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J135:J198" si="7">IF(I135="","",1440-I135)</f>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -6122,11 +6171,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6144,11 +6193,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I199:I262" si="8">IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J199:J262" si="9">IF(I199="","",1440-I199)</f>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -7530,11 +7579,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7552,11 +7601,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I263:I326" si="10">IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J263:J326" si="11">IF(I263="","",1440-I263)</f>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8938,11 +8987,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8960,11 +9009,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I327:I390" si="12">IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J327:J390" si="13">IF(I327="","",1440-I327)</f>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -10346,11 +10395,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10368,11 +10417,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I391:I402" si="14">IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J391:J402" si="15">IF(I391="","",1440-I391)</f>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10600,6 +10649,28 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10609,21 +10680,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J402">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K402" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L402" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M402" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="462" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5916DC3E-8C0F-4D0B-81BB-12763B5014E1}"/>
+  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8224C896-3B44-4800-8755-DC5A3F24EA50}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2681,7 +2681,7 @@
         <v>200</v>
       </c>
       <c r="G41" s="14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="14">
         <v>315</v>
@@ -2703,7 +2703,9 @@
       <c r="M41" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N41" s="17"/>
+      <c r="N41" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
@@ -2752,25 +2754,47 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>400</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>350</v>
+      </c>
+      <c r="G43" s="14">
+        <v>7</v>
+      </c>
+      <c r="H43" s="14">
+        <v>250</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="477" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8224C896-3B44-4800-8755-DC5A3F24EA50}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83AEF3BE-9E13-4243-B0BD-ADD30656D875}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>friends birthday</t>
+  </si>
+  <si>
+    <t>need more focus in coding</t>
   </si>
 </sst>
 </file>
@@ -2798,26 +2801,50 @@
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>395</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>50</v>
+      </c>
+      <c r="E44" s="14">
+        <v>190</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>300</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>305</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
@@ -10724,7 +10751,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83AEF3BE-9E13-4243-B0BD-ADD30656D875}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A27E08DC-5BD6-47EE-859B-733343D988F5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -294,6 +294,12 @@
   </si>
   <si>
     <t>need more focus in coding</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>c++  is too weak</t>
   </si>
 </sst>
 </file>
@@ -2847,29 +2853,53 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>60</v>
+      </c>
+      <c r="E45" s="14">
+        <v>150</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>280</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
+      <c r="A46" s="8"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A27E08DC-5BD6-47EE-859B-733343D988F5}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F642C97F-C128-407A-A699-B2171D0C3C8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2899,25 +2899,47 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="14">
+        <v>380</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>100</v>
+      </c>
+      <c r="E46" s="14">
+        <v>80</v>
+      </c>
+      <c r="F46" s="14">
+        <v>150</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>380</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="531" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F642C97F-C128-407A-A699-B2171D0C3C8E}"/>
+  <xr:revisionPtr revIDLastSave="707" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24955319-0E5C-4897-9775-5098F30B166F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -300,6 +300,39 @@
   </si>
   <si>
     <t>c++  is too weak</t>
+  </si>
+  <si>
+    <t>exam went well</t>
+  </si>
+  <si>
+    <t>first mid term exam</t>
+  </si>
+  <si>
+    <t>went to jalandhar</t>
+  </si>
+  <si>
+    <t>spend whole day in train</t>
+  </si>
+  <si>
+    <t>spend half day in train and then went to eastwood</t>
+  </si>
+  <si>
+    <t>went ahmedabad to catch train</t>
+  </si>
+  <si>
+    <t>a normal day at home</t>
+  </si>
+  <si>
+    <t>outing with friends</t>
+  </si>
+  <si>
+    <t>going on a trip with friends</t>
+  </si>
+  <si>
+    <t>went khatu shyam jaipur</t>
+  </si>
+  <si>
+    <t>spend day in udaipur</t>
   </si>
 </sst>
 </file>
@@ -956,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N402"/>
+  <dimension ref="A1:N414"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1110,11 +1143,11 @@
         <v>340</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I70" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I82" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1260</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J70" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J82" si="1">IF(I6="","",1440-I6)</f>
         <v>180</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -2943,290 +2976,598 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>600</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" ref="I47" si="4">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <v>1030</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" ref="J47" si="5">IF(I47="","",1440-I47)</f>
+        <v>410</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B48" s="14">
+        <v>280</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>800</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B49" s="14">
+        <v>380</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>750</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>310</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B50" s="14">
+        <v>430</v>
+      </c>
+      <c r="C50" s="14">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>200</v>
+      </c>
+      <c r="G50" s="14">
+        <v>4</v>
+      </c>
+      <c r="H50" s="14">
+        <v>450</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+        <v>330</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="17"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>350</v>
+      </c>
+      <c r="G51" s="14">
+        <v>7</v>
+      </c>
+      <c r="H51" s="14">
+        <v>400</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B52" s="14">
+        <v>400</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>350</v>
+      </c>
+      <c r="G52" s="14">
+        <v>7</v>
+      </c>
+      <c r="H52" s="14">
+        <v>350</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>310</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B53" s="14">
+        <v>300</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>660</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B54" s="14">
+        <v>400</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>600</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>440</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B55" s="14">
+        <v>380</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>650</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B56" s="14">
+        <v>415</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>180</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>540</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+        <v>305</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="17"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B57" s="14">
+        <v>420</v>
+      </c>
+      <c r="C57" s="14">
+        <v>15</v>
+      </c>
+      <c r="D57" s="14">
+        <v>150</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>420</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+        <v>435</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B58" s="14">
+        <v>400</v>
+      </c>
+      <c r="C58" s="14">
+        <v>20</v>
+      </c>
+      <c r="D58" s="14">
+        <v>165</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>450</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>405</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B59" s="14">
+        <v>450</v>
+      </c>
+      <c r="C59" s="14">
+        <v>20</v>
+      </c>
+      <c r="D59" s="14">
+        <v>200</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>350</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
@@ -3480,11 +3821,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" ref="I71:I134" si="4">IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" ref="J71:J134" si="5">IF(I71="","",1440-I71)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3502,11 +3843,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3524,11 +3865,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3546,11 +3887,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3568,11 +3909,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3590,11 +3931,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3612,11 +3953,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3634,11 +3975,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3656,11 +3997,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3678,11 +4019,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3700,11 +4041,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3722,11 +4063,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3744,11 +4085,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I83:I146" si="6">IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J83:J146" si="7">IF(I83="","",1440-I83)</f>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3766,11 +4107,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3788,11 +4129,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3810,11 +4151,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3832,11 +4173,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3854,11 +4195,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3876,11 +4217,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3898,11 +4239,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3920,11 +4261,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3942,11 +4283,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3964,11 +4305,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3986,11 +4327,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4008,11 +4349,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4030,11 +4371,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4052,11 +4393,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4074,11 +4415,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4096,11 +4437,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4118,11 +4459,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4140,11 +4481,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4162,11 +4503,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4184,11 +4525,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4206,11 +4547,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4228,11 +4569,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4250,11 +4591,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4272,11 +4613,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4294,11 +4635,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4316,11 +4657,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4338,11 +4679,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4360,11 +4701,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4382,11 +4723,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4404,11 +4745,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4426,11 +4767,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4448,11 +4789,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4470,11 +4811,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4492,11 +4833,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4514,11 +4855,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4536,11 +4877,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4558,11 +4899,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4580,11 +4921,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4602,11 +4943,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4624,11 +4965,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4646,11 +4987,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4668,11 +5009,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4690,11 +5031,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4712,11 +5053,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4734,11 +5075,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4756,11 +5097,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4778,11 +5119,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4800,11 +5141,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4822,11 +5163,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4844,11 +5185,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4866,11 +5207,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4888,11 +5229,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" ref="I135:I198" si="6">IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" ref="J135:J198" si="7">IF(I135="","",1440-I135)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5152,11 +5493,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I147:I210" si="8">IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J147:J210" si="9">IF(I147="","",1440-I147)</f>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5174,11 +5515,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5196,11 +5537,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5218,11 +5559,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5240,11 +5581,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5262,11 +5603,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5284,11 +5625,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5306,11 +5647,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5328,11 +5669,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5350,11 +5691,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5372,11 +5713,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5394,11 +5735,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5416,11 +5757,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5438,11 +5779,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5460,11 +5801,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5482,11 +5823,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5504,11 +5845,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5526,11 +5867,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5548,11 +5889,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5570,11 +5911,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5592,11 +5933,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5614,11 +5955,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5636,11 +5977,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5658,11 +5999,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5680,11 +6021,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5702,11 +6043,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5724,11 +6065,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5746,11 +6087,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5768,11 +6109,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5790,11 +6131,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5812,11 +6153,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5834,11 +6175,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5856,11 +6197,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5878,11 +6219,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5900,11 +6241,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5922,11 +6263,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5944,11 +6285,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5966,11 +6307,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5988,11 +6329,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6010,11 +6351,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6032,11 +6373,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6054,11 +6395,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6076,11 +6417,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6098,11 +6439,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6120,11 +6461,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6142,11 +6483,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6164,11 +6505,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6186,11 +6527,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6208,11 +6549,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6230,11 +6571,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6252,11 +6593,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6274,11 +6615,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6296,11 +6637,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" ref="I199:I262" si="8">IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" ref="J199:J262" si="9">IF(I199="","",1440-I199)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6560,11 +6901,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I211:I274" si="10">IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J211:J274" si="11">IF(I211="","",1440-I211)</f>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6582,11 +6923,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6604,11 +6945,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6626,11 +6967,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6648,11 +6989,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6670,11 +7011,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6692,11 +7033,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6714,11 +7055,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6736,11 +7077,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6758,11 +7099,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6780,11 +7121,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6802,11 +7143,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6824,11 +7165,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6846,11 +7187,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6868,11 +7209,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6890,11 +7231,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6912,11 +7253,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6934,11 +7275,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6956,11 +7297,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6978,11 +7319,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7000,11 +7341,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7022,11 +7363,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7044,11 +7385,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7066,11 +7407,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7088,11 +7429,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7110,11 +7451,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7132,11 +7473,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7154,11 +7495,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7176,11 +7517,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7198,11 +7539,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7220,11 +7561,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7242,11 +7583,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7264,11 +7605,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7286,11 +7627,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7308,11 +7649,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7330,11 +7671,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7352,11 +7693,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7374,11 +7715,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7396,11 +7737,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7418,11 +7759,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7440,11 +7781,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7462,11 +7803,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7484,11 +7825,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7506,11 +7847,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7528,11 +7869,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7550,11 +7891,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7572,11 +7913,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7594,11 +7935,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7616,11 +7957,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7638,11 +7979,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7660,11 +8001,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7682,11 +8023,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7704,11 +8045,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" ref="I263:I326" si="10">IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" ref="J263:J326" si="11">IF(I263="","",1440-I263)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7968,11 +8309,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I275:I338" si="12">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J275:J338" si="13">IF(I275="","",1440-I275)</f>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7990,11 +8331,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8012,11 +8353,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8034,11 +8375,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8056,11 +8397,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8078,11 +8419,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8100,11 +8441,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8122,11 +8463,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8144,11 +8485,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8166,11 +8507,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8188,11 +8529,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8210,11 +8551,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8232,11 +8573,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8254,11 +8595,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8276,11 +8617,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8298,11 +8639,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8320,11 +8661,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8342,11 +8683,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8364,11 +8705,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8386,11 +8727,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8408,11 +8749,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8430,11 +8771,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8452,11 +8793,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8474,11 +8815,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8496,11 +8837,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8518,11 +8859,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8540,11 +8881,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8562,11 +8903,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8584,11 +8925,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8606,11 +8947,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8628,11 +8969,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8650,11 +8991,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8672,11 +9013,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8694,11 +9035,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8716,11 +9057,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8738,11 +9079,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8760,11 +9101,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8782,11 +9123,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8804,11 +9145,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8826,11 +9167,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8848,11 +9189,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8870,11 +9211,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8892,11 +9233,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8914,11 +9255,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8936,11 +9277,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8958,11 +9299,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8980,11 +9321,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9002,11 +9343,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9024,11 +9365,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9046,11 +9387,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9068,11 +9409,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9090,11 +9431,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9112,11 +9453,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" ref="I327:I390" si="12">IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" ref="J327:J390" si="13">IF(I327="","",1440-I327)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9376,11 +9717,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I339:I402" si="14">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J339:J402" si="15">IF(I339="","",1440-I339)</f>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9398,11 +9739,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9420,11 +9761,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9442,11 +9783,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9464,11 +9805,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9486,11 +9827,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9508,11 +9849,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9530,11 +9871,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9552,11 +9893,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9574,11 +9915,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9596,11 +9937,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9618,11 +9959,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9640,11 +9981,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9662,11 +10003,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9684,11 +10025,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9706,11 +10047,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9728,11 +10069,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9750,11 +10091,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9772,11 +10113,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9794,11 +10135,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9816,11 +10157,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9838,11 +10179,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9860,11 +10201,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9882,11 +10223,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9904,11 +10245,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9926,11 +10267,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9948,11 +10289,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9970,11 +10311,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9992,11 +10333,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10014,11 +10355,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10036,11 +10377,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10058,11 +10399,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10080,11 +10421,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10102,11 +10443,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10124,11 +10465,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10146,11 +10487,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10168,11 +10509,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10190,11 +10531,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10212,11 +10553,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10234,11 +10575,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10256,11 +10597,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10278,11 +10619,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10300,11 +10641,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10322,11 +10663,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10344,11 +10685,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10366,11 +10707,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10388,11 +10729,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10410,11 +10751,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10432,11 +10773,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10454,11 +10795,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10476,11 +10817,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10498,11 +10839,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10520,11 +10861,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" ref="I391:I402" si="14">IF(SUM(B391:F391,H391)=0,"",SUM(B391:F391,H391))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" ref="J391:J402" si="15">IF(I391="","",1440-I391)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10774,6 +11115,270 @@
       <c r="M402" s="16"/>
       <c r="N402" s="17"/>
     </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" ref="I403:I414" si="16">IF(SUM(B403:F403,H403)=0,"",SUM(B403:F403,H403))</f>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" ref="J403:J414" si="17">IF(I403="","",1440-I403)</f>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A406" s="13"/>
+      <c r="B406" s="14"/>
+      <c r="C406" s="14"/>
+      <c r="D406" s="14"/>
+      <c r="E406" s="14"/>
+      <c r="F406" s="14"/>
+      <c r="G406" s="14"/>
+      <c r="H406" s="14"/>
+      <c r="I406" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J406" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K406" s="16"/>
+      <c r="L406" s="16"/>
+      <c r="M406" s="16"/>
+      <c r="N406" s="17"/>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A407" s="13"/>
+      <c r="B407" s="14"/>
+      <c r="C407" s="14"/>
+      <c r="D407" s="14"/>
+      <c r="E407" s="14"/>
+      <c r="F407" s="14"/>
+      <c r="G407" s="14"/>
+      <c r="H407" s="14"/>
+      <c r="I407" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J407" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K407" s="16"/>
+      <c r="L407" s="16"/>
+      <c r="M407" s="16"/>
+      <c r="N407" s="17"/>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A408" s="13"/>
+      <c r="B408" s="14"/>
+      <c r="C408" s="14"/>
+      <c r="D408" s="14"/>
+      <c r="E408" s="14"/>
+      <c r="F408" s="14"/>
+      <c r="G408" s="14"/>
+      <c r="H408" s="14"/>
+      <c r="I408" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J408" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K408" s="16"/>
+      <c r="L408" s="16"/>
+      <c r="M408" s="16"/>
+      <c r="N408" s="17"/>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A409" s="13"/>
+      <c r="B409" s="14"/>
+      <c r="C409" s="14"/>
+      <c r="D409" s="14"/>
+      <c r="E409" s="14"/>
+      <c r="F409" s="14"/>
+      <c r="G409" s="14"/>
+      <c r="H409" s="14"/>
+      <c r="I409" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J409" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K409" s="16"/>
+      <c r="L409" s="16"/>
+      <c r="M409" s="16"/>
+      <c r="N409" s="17"/>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A410" s="13"/>
+      <c r="B410" s="14"/>
+      <c r="C410" s="14"/>
+      <c r="D410" s="14"/>
+      <c r="E410" s="14"/>
+      <c r="F410" s="14"/>
+      <c r="G410" s="14"/>
+      <c r="H410" s="14"/>
+      <c r="I410" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J410" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K410" s="16"/>
+      <c r="L410" s="16"/>
+      <c r="M410" s="16"/>
+      <c r="N410" s="17"/>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A411" s="13"/>
+      <c r="B411" s="14"/>
+      <c r="C411" s="14"/>
+      <c r="D411" s="14"/>
+      <c r="E411" s="14"/>
+      <c r="F411" s="14"/>
+      <c r="G411" s="14"/>
+      <c r="H411" s="14"/>
+      <c r="I411" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J411" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K411" s="16"/>
+      <c r="L411" s="16"/>
+      <c r="M411" s="16"/>
+      <c r="N411" s="17"/>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A412" s="13"/>
+      <c r="B412" s="14"/>
+      <c r="C412" s="14"/>
+      <c r="D412" s="14"/>
+      <c r="E412" s="14"/>
+      <c r="F412" s="14"/>
+      <c r="G412" s="14"/>
+      <c r="H412" s="14"/>
+      <c r="I412" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J412" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K412" s="16"/>
+      <c r="L412" s="16"/>
+      <c r="M412" s="16"/>
+      <c r="N412" s="17"/>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A413" s="13"/>
+      <c r="B413" s="14"/>
+      <c r="C413" s="14"/>
+      <c r="D413" s="14"/>
+      <c r="E413" s="14"/>
+      <c r="F413" s="14"/>
+      <c r="G413" s="14"/>
+      <c r="H413" s="14"/>
+      <c r="I413" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J413" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K413" s="16"/>
+      <c r="L413" s="16"/>
+      <c r="M413" s="16"/>
+      <c r="N413" s="17"/>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A414" s="13"/>
+      <c r="B414" s="14"/>
+      <c r="C414" s="14"/>
+      <c r="D414" s="14"/>
+      <c r="E414" s="14"/>
+      <c r="F414" s="14"/>
+      <c r="G414" s="14"/>
+      <c r="H414" s="14"/>
+      <c r="I414" s="15" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="J414" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="K414" s="16"/>
+      <c r="L414" s="16"/>
+      <c r="M414" s="16"/>
+      <c r="N414" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10783,21 +11388,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J402">
+  <conditionalFormatting sqref="J6:J414">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K402" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K414" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L402" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L414" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M402" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M414" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="707" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24955319-0E5C-4897-9775-5098F30B166F}"/>
+  <xr:revisionPtr revIDLastSave="838" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9385B06-BA66-4CC9-A3B1-06FFF0F111E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -333,6 +333,27 @@
   </si>
   <si>
     <t>spend day in udaipur</t>
+  </si>
+  <si>
+    <t>enjoyed garba night</t>
+  </si>
+  <si>
+    <t>visited mata rani temple</t>
+  </si>
+  <si>
+    <t>last exam</t>
+  </si>
+  <si>
+    <t>major protest held at our university.</t>
+  </si>
+  <si>
+    <t>travelling to home</t>
+  </si>
+  <si>
+    <t>first day at home</t>
+  </si>
+  <si>
+    <t>met my all friends</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N414"/>
+  <dimension ref="A1:N419"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1143,11 +1164,11 @@
         <v>340</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I82" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I87" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1260</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J82" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J87" si="1">IF(I6="","",1440-I6)</f>
         <v>180</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -2975,15 +2996,15 @@
       </c>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
-        <v>46297</v>
+        <v>46292</v>
       </c>
       <c r="B47" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C47" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D47" s="14">
         <v>0</v>
@@ -3001,814 +3022,1072 @@
         <v>600</v>
       </c>
       <c r="I47" s="15">
-        <f t="shared" ref="I47" si="4">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
-        <v>1030</v>
+        <f t="shared" ref="I47:I51" si="4">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <v>900</v>
       </c>
       <c r="J47" s="15">
-        <f t="shared" ref="J47" si="5">IF(I47="","",1440-I47)</f>
-        <v>410</v>
+        <f t="shared" ref="J47:J51" si="5">IF(I47="","",1440-I47)</f>
+        <v>540</v>
       </c>
       <c r="K47" s="16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L47" s="16" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="M47" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="14">
+        <v>300</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>700</v>
+      </c>
+      <c r="I48" s="15">
+        <f t="shared" si="4"/>
+        <v>1000</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="5"/>
+        <v>440</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="14">
+        <v>380</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>800</v>
+      </c>
+      <c r="I49" s="15">
+        <f t="shared" ref="I49" si="6">IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <v>1180</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" ref="J49" si="7">IF(I49="","",1440-I49)</f>
+        <v>260</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="14">
+        <v>360</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>760</v>
+      </c>
+      <c r="I50" s="15">
+        <f t="shared" si="4"/>
+        <v>1120</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="5"/>
+        <v>320</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>700</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="4"/>
+        <v>1150</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="5"/>
+        <v>290</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="14">
+        <v>400</v>
+      </c>
+      <c r="C52" s="14">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>600</v>
+      </c>
+      <c r="I52" s="15">
+        <f t="shared" ref="I52" si="8">IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
+        <v>1030</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" ref="J52" si="9">IF(I52="","",1440-I52)</f>
+        <v>410</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
         <v>46298</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B53" s="14">
         <v>280</v>
       </c>
-      <c r="C48" s="14">
-        <v>0</v>
-      </c>
-      <c r="D48" s="14">
-        <v>0</v>
-      </c>
-      <c r="E48" s="14">
-        <v>0</v>
-      </c>
-      <c r="F48" s="14">
-        <v>0</v>
-      </c>
-      <c r="G48" s="14">
-        <v>0</v>
-      </c>
-      <c r="H48" s="14">
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
         <v>800</v>
       </c>
-      <c r="I48" s="15">
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K48" s="16" t="s">
+      <c r="K53" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L48" s="16" t="s">
+      <c r="L53" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M48" s="16" t="s">
+      <c r="M53" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N48" s="17" t="s">
+      <c r="N53" s="17" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
         <v>46299</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B54" s="14">
         <v>380</v>
       </c>
-      <c r="C49" s="14">
-        <v>0</v>
-      </c>
-      <c r="D49" s="14">
-        <v>0</v>
-      </c>
-      <c r="E49" s="14">
-        <v>0</v>
-      </c>
-      <c r="F49" s="14">
-        <v>0</v>
-      </c>
-      <c r="G49" s="14">
-        <v>0</v>
-      </c>
-      <c r="H49" s="14">
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
         <v>750</v>
       </c>
-      <c r="I49" s="15">
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K49" s="16" t="s">
+      <c r="K54" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L49" s="16" t="s">
+      <c r="L54" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M49" s="16" t="s">
+      <c r="M54" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N49" s="17" t="s">
+      <c r="N54" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
         <v>46300</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B55" s="14">
         <v>430</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C55" s="14">
         <v>30</v>
       </c>
-      <c r="D50" s="14">
-        <v>0</v>
-      </c>
-      <c r="E50" s="14">
-        <v>0</v>
-      </c>
-      <c r="F50" s="14">
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
         <v>200</v>
       </c>
-      <c r="G50" s="14">
+      <c r="G55" s="14">
         <v>4</v>
       </c>
-      <c r="H50" s="14">
+      <c r="H55" s="14">
         <v>450</v>
       </c>
-      <c r="I50" s="15">
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="J50" s="15">
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
-      <c r="K50" s="16" t="s">
+      <c r="K55" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L50" s="16" t="s">
+      <c r="L55" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M50" s="16" t="s">
+      <c r="M55" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+      <c r="N55" s="17"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
         <v>46301</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B56" s="14">
         <v>420</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C56" s="14">
         <v>30</v>
       </c>
-      <c r="D51" s="14">
-        <v>0</v>
-      </c>
-      <c r="E51" s="14">
-        <v>0</v>
-      </c>
-      <c r="F51" s="14">
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
         <v>350</v>
       </c>
-      <c r="G51" s="14">
+      <c r="G56" s="14">
         <v>7</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H56" s="14">
         <v>400</v>
       </c>
-      <c r="I51" s="15">
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K51" s="16" t="s">
+      <c r="K56" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L51" s="16" t="s">
+      <c r="L56" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M51" s="16" t="s">
+      <c r="M56" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N51" s="17" t="s">
+      <c r="N56" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
         <v>46302</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B57" s="14">
         <v>400</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C57" s="14">
         <v>30</v>
       </c>
-      <c r="D52" s="14">
-        <v>0</v>
-      </c>
-      <c r="E52" s="14">
-        <v>0</v>
-      </c>
-      <c r="F52" s="14">
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
         <v>350</v>
       </c>
-      <c r="G52" s="14">
+      <c r="G57" s="14">
         <v>7</v>
       </c>
-      <c r="H52" s="14">
+      <c r="H57" s="14">
         <v>350</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="J52" s="15">
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="K52" s="16" t="s">
+      <c r="K57" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L52" s="16" t="s">
+      <c r="L57" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M52" s="16" t="s">
+      <c r="M57" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N52" s="17" t="s">
+      <c r="N57" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
         <v>46303</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B58" s="14">
         <v>300</v>
       </c>
-      <c r="C53" s="14">
-        <v>0</v>
-      </c>
-      <c r="D53" s="14">
-        <v>0</v>
-      </c>
-      <c r="E53" s="14">
-        <v>0</v>
-      </c>
-      <c r="F53" s="14">
-        <v>0</v>
-      </c>
-      <c r="G53" s="14">
-        <v>0</v>
-      </c>
-      <c r="H53" s="14">
+      <c r="C58" s="14">
+        <v>0</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
         <v>660</v>
       </c>
-      <c r="I53" s="15">
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J53" s="15">
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K53" s="16" t="s">
+      <c r="K58" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L53" s="16" t="s">
+      <c r="L58" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M53" s="16" t="s">
+      <c r="M58" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N53" s="17" t="s">
+      <c r="N58" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="8">
         <v>46304</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B59" s="14">
         <v>400</v>
       </c>
-      <c r="C54" s="14">
-        <v>0</v>
-      </c>
-      <c r="D54" s="14">
-        <v>0</v>
-      </c>
-      <c r="E54" s="14">
-        <v>0</v>
-      </c>
-      <c r="F54" s="14">
-        <v>0</v>
-      </c>
-      <c r="G54" s="14">
-        <v>0</v>
-      </c>
-      <c r="H54" s="14">
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
         <v>600</v>
       </c>
-      <c r="I54" s="15">
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="J54" s="15">
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
         <v>440</v>
       </c>
-      <c r="K54" s="16" t="s">
+      <c r="K59" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="L54" s="16" t="s">
+      <c r="L59" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M54" s="16" t="s">
+      <c r="M59" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N54" s="17" t="s">
+      <c r="N59" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="8">
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
         <v>46305</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B60" s="14">
         <v>380</v>
       </c>
-      <c r="C55" s="14">
-        <v>0</v>
-      </c>
-      <c r="D55" s="14">
-        <v>0</v>
-      </c>
-      <c r="E55" s="14">
-        <v>0</v>
-      </c>
-      <c r="F55" s="14">
-        <v>0</v>
-      </c>
-      <c r="G55" s="14">
-        <v>0</v>
-      </c>
-      <c r="H55" s="14">
+      <c r="C60" s="14">
+        <v>0</v>
+      </c>
+      <c r="D60" s="14">
+        <v>0</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
         <v>650</v>
       </c>
-      <c r="I55" s="15">
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
-      <c r="J55" s="15">
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
         <v>410</v>
       </c>
-      <c r="K55" s="16" t="s">
+      <c r="K60" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L55" s="16" t="s">
+      <c r="L60" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="M55" s="16" t="s">
+      <c r="M60" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N55" s="17" t="s">
+      <c r="N60" s="17" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
         <v>46306</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B61" s="14">
         <v>415</v>
       </c>
-      <c r="C56" s="14">
-        <v>0</v>
-      </c>
-      <c r="D56" s="14">
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
         <v>180</v>
       </c>
-      <c r="E56" s="14">
-        <v>0</v>
-      </c>
-      <c r="F56" s="14">
-        <v>0</v>
-      </c>
-      <c r="G56" s="14">
-        <v>0</v>
-      </c>
-      <c r="H56" s="14">
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
         <v>540</v>
       </c>
-      <c r="I56" s="15">
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
         <v>1135</v>
       </c>
-      <c r="J56" s="15">
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
         <v>305</v>
       </c>
-      <c r="K56" s="16" t="s">
+      <c r="K61" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L56" s="16" t="s">
+      <c r="L61" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M56" s="16" t="s">
+      <c r="M61" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
+      <c r="N61" s="17"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
         <v>46307</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B62" s="14">
         <v>420</v>
       </c>
-      <c r="C57" s="14">
+      <c r="C62" s="14">
         <v>15</v>
       </c>
-      <c r="D57" s="14">
+      <c r="D62" s="14">
         <v>150</v>
       </c>
-      <c r="E57" s="14">
-        <v>0</v>
-      </c>
-      <c r="F57" s="14">
-        <v>0</v>
-      </c>
-      <c r="G57" s="14">
-        <v>0</v>
-      </c>
-      <c r="H57" s="14">
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
         <v>420</v>
       </c>
-      <c r="I57" s="15">
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
-      <c r="J57" s="15">
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
         <v>435</v>
       </c>
-      <c r="K57" s="16" t="s">
+      <c r="K62" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L57" s="16" t="s">
+      <c r="L62" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M57" s="16" t="s">
+      <c r="M62" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N57" s="17" t="s">
+      <c r="N62" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
         <v>46308</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B63" s="14">
         <v>400</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C63" s="14">
         <v>20</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D63" s="14">
         <v>165</v>
       </c>
-      <c r="E58" s="14">
-        <v>0</v>
-      </c>
-      <c r="F58" s="14">
-        <v>0</v>
-      </c>
-      <c r="G58" s="14">
-        <v>0</v>
-      </c>
-      <c r="H58" s="14">
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
         <v>450</v>
       </c>
-      <c r="I58" s="15">
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
-      <c r="J58" s="15">
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="K58" s="16" t="s">
+      <c r="K63" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L58" s="16" t="s">
+      <c r="L63" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M58" s="16" t="s">
+      <c r="M63" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N58" s="17" t="s">
+      <c r="N63" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
         <v>46309</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B64" s="14">
         <v>450</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C64" s="14">
         <v>20</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D64" s="14">
         <v>200</v>
       </c>
-      <c r="E59" s="14">
-        <v>0</v>
-      </c>
-      <c r="F59" s="14">
-        <v>0</v>
-      </c>
-      <c r="G59" s="14">
-        <v>0</v>
-      </c>
-      <c r="H59" s="14">
+      <c r="E64" s="14">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
         <v>350</v>
       </c>
-      <c r="I59" s="15">
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="J59" s="15">
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="K59" s="16" t="s">
+      <c r="K64" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="L59" s="16" t="s">
+      <c r="L64" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="M59" s="16" t="s">
+      <c r="M64" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N59" s="17" t="s">
+      <c r="N64" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="14">
+        <v>420</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>200</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>490</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+        <v>300</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N65" s="17"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="14">
+        <v>400</v>
+      </c>
+      <c r="C66" s="14">
+        <v>0</v>
+      </c>
+      <c r="D66" s="14">
+        <v>180</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>520</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N66" s="17"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="14">
+        <v>410</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>150</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>500</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="14">
+        <v>400</v>
+      </c>
+      <c r="C68" s="14">
+        <v>20</v>
+      </c>
+      <c r="D68" s="14">
+        <v>0</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>650</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="14">
+        <v>430</v>
+      </c>
+      <c r="C69" s="14">
+        <v>0</v>
+      </c>
+      <c r="D69" s="14">
+        <v>0</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>200</v>
+      </c>
+      <c r="G69" s="14">
+        <v>4</v>
+      </c>
+      <c r="H69" s="14">
+        <v>460</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="14">
+        <v>380</v>
+      </c>
+      <c r="C70" s="14">
+        <v>0</v>
+      </c>
+      <c r="D70" s="14">
+        <v>110</v>
+      </c>
+      <c r="E70" s="14">
+        <v>60</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>350</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
@@ -4085,11 +4364,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" ref="I83:I146" si="6">IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" ref="J83:J146" si="7">IF(I83="","",1440-I83)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -4107,11 +4386,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -4129,11 +4408,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -4151,11 +4430,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4173,11 +4452,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4195,11 +4474,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I88:I151" si="10">IF(SUM(B88:F88,H88)=0,"",SUM(B88:F88,H88))</f>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J88:J151" si="11">IF(I88="","",1440-I88)</f>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4217,11 +4496,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4239,11 +4518,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4261,11 +4540,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4283,11 +4562,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4305,11 +4584,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4327,11 +4606,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4349,11 +4628,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4371,11 +4650,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4393,11 +4672,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4415,11 +4694,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4437,11 +4716,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4459,11 +4738,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4481,11 +4760,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4503,11 +4782,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4525,11 +4804,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4547,11 +4826,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4569,11 +4848,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4591,11 +4870,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4613,11 +4892,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4635,11 +4914,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4657,11 +4936,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4679,11 +4958,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4701,11 +4980,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4723,11 +5002,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4745,11 +5024,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4767,11 +5046,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4789,11 +5068,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4811,11 +5090,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4833,11 +5112,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4855,11 +5134,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4877,11 +5156,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4899,11 +5178,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4921,11 +5200,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4943,11 +5222,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4965,11 +5244,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4987,11 +5266,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -5009,11 +5288,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -5031,11 +5310,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -5053,11 +5332,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -5075,11 +5354,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -5097,11 +5376,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5119,11 +5398,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -5141,11 +5420,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -5163,11 +5442,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5185,11 +5464,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5207,11 +5486,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5229,11 +5508,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5251,11 +5530,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5273,11 +5552,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5295,11 +5574,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5317,11 +5596,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5339,11 +5618,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5361,11 +5640,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5383,11 +5662,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5405,11 +5684,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5427,11 +5706,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5449,11 +5728,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5471,11 +5750,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5493,11 +5772,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" ref="I147:I210" si="8">IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" ref="J147:J210" si="9">IF(I147="","",1440-I147)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5515,11 +5794,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5537,11 +5816,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5559,11 +5838,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5581,11 +5860,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5603,11 +5882,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I152:I215" si="12">IF(SUM(B152:F152,H152)=0,"",SUM(B152:F152,H152))</f>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J152:J215" si="13">IF(I152="","",1440-I152)</f>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5625,11 +5904,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5647,11 +5926,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5669,11 +5948,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5691,11 +5970,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5713,11 +5992,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5735,11 +6014,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5757,11 +6036,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5779,11 +6058,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5801,11 +6080,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5823,11 +6102,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5845,11 +6124,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5867,11 +6146,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5889,11 +6168,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5911,11 +6190,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5933,11 +6212,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5955,11 +6234,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5977,11 +6256,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5999,11 +6278,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6021,11 +6300,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6043,11 +6322,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6065,11 +6344,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6087,11 +6366,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6109,11 +6388,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6131,11 +6410,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6153,11 +6432,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6175,11 +6454,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6197,11 +6476,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6219,11 +6498,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6241,11 +6520,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6263,11 +6542,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6285,11 +6564,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6307,11 +6586,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6329,11 +6608,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6351,11 +6630,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6373,11 +6652,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6395,11 +6674,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6417,11 +6696,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6439,11 +6718,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6461,11 +6740,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6483,11 +6762,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6505,11 +6784,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6527,11 +6806,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6549,11 +6828,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6571,11 +6850,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6593,11 +6872,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6615,11 +6894,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6637,11 +6916,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6659,11 +6938,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6681,11 +6960,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6703,11 +6982,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6725,11 +7004,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6747,11 +7026,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6769,11 +7048,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6791,11 +7070,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6813,11 +7092,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6835,11 +7114,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6857,11 +7136,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6879,11 +7158,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6901,11 +7180,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" ref="I211:I274" si="10">IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" ref="J211:J274" si="11">IF(I211="","",1440-I211)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6923,11 +7202,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6945,11 +7224,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6967,11 +7246,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6989,11 +7268,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7011,11 +7290,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I216:I279" si="14">IF(SUM(B216:F216,H216)=0,"",SUM(B216:F216,H216))</f>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J216:J279" si="15">IF(I216="","",1440-I216)</f>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7033,11 +7312,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7055,11 +7334,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7077,11 +7356,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7099,11 +7378,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7121,11 +7400,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7143,11 +7422,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7165,11 +7444,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7187,11 +7466,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7209,11 +7488,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7231,11 +7510,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7253,11 +7532,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7275,11 +7554,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7297,11 +7576,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7319,11 +7598,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7341,11 +7620,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7363,11 +7642,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7385,11 +7664,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7407,11 +7686,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7429,11 +7708,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7451,11 +7730,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7473,11 +7752,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7495,11 +7774,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7517,11 +7796,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7539,11 +7818,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7561,11 +7840,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7583,11 +7862,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7605,11 +7884,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7627,11 +7906,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7649,11 +7928,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7671,11 +7950,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7693,11 +7972,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7715,11 +7994,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7737,11 +8016,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7759,11 +8038,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7781,11 +8060,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7803,11 +8082,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7825,11 +8104,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7847,11 +8126,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7869,11 +8148,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7891,11 +8170,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7913,11 +8192,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7935,11 +8214,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7957,11 +8236,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7979,11 +8258,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8001,11 +8280,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8023,11 +8302,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8045,11 +8324,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8067,11 +8346,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8089,11 +8368,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8111,11 +8390,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8133,11 +8412,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8155,11 +8434,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8177,11 +8456,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8199,11 +8478,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8221,11 +8500,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8243,11 +8522,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8265,11 +8544,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8287,11 +8566,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8309,11 +8588,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" ref="I275:I338" si="12">IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" ref="J275:J338" si="13">IF(I275="","",1440-I275)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8331,11 +8610,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8353,11 +8632,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8375,11 +8654,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8397,11 +8676,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8419,11 +8698,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I280:I343" si="16">IF(SUM(B280:F280,H280)=0,"",SUM(B280:F280,H280))</f>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J280:J343" si="17">IF(I280="","",1440-I280)</f>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8441,11 +8720,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8463,11 +8742,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8485,11 +8764,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8507,11 +8786,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8529,11 +8808,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8551,11 +8830,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8573,11 +8852,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8595,11 +8874,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8617,11 +8896,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8639,11 +8918,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8661,11 +8940,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8683,11 +8962,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8705,11 +8984,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8727,11 +9006,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8749,11 +9028,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8771,11 +9050,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8793,11 +9072,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8815,11 +9094,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8837,11 +9116,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8859,11 +9138,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8881,11 +9160,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8903,11 +9182,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8925,11 +9204,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8947,11 +9226,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8969,11 +9248,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8991,11 +9270,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9013,11 +9292,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9035,11 +9314,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9057,11 +9336,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9079,11 +9358,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9101,11 +9380,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9123,11 +9402,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9145,11 +9424,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9167,11 +9446,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9189,11 +9468,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9211,11 +9490,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9233,11 +9512,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9255,11 +9534,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9277,11 +9556,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9299,11 +9578,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9321,11 +9600,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9343,11 +9622,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9365,11 +9644,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9387,11 +9666,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9409,11 +9688,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9431,11 +9710,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9453,11 +9732,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9475,11 +9754,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9497,11 +9776,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9519,11 +9798,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9541,11 +9820,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9563,11 +9842,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9585,11 +9864,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9607,11 +9886,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9629,11 +9908,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9651,11 +9930,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9673,11 +9952,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9695,11 +9974,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9717,11 +9996,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" ref="I339:I402" si="14">IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" ref="J339:J402" si="15">IF(I339="","",1440-I339)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9739,11 +10018,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9761,11 +10040,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9783,11 +10062,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9805,11 +10084,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9827,11 +10106,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I344:I407" si="18">IF(SUM(B344:F344,H344)=0,"",SUM(B344:F344,H344))</f>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J344:J407" si="19">IF(I344="","",1440-I344)</f>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9849,11 +10128,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9871,11 +10150,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9893,11 +10172,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9915,11 +10194,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9937,11 +10216,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9959,11 +10238,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9981,11 +10260,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10003,11 +10282,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10025,11 +10304,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10047,11 +10326,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10069,11 +10348,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10091,11 +10370,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10113,11 +10392,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10135,11 +10414,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10157,11 +10436,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10179,11 +10458,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10201,11 +10480,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10223,11 +10502,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10245,11 +10524,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10267,11 +10546,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10289,11 +10568,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10311,11 +10590,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10333,11 +10612,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10355,11 +10634,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10377,11 +10656,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10399,11 +10678,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10421,11 +10700,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10443,11 +10722,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10465,11 +10744,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10487,11 +10766,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10509,11 +10788,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10531,11 +10810,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10553,11 +10832,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10575,11 +10854,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10597,11 +10876,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10619,11 +10898,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10641,11 +10920,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10663,11 +10942,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10685,11 +10964,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10707,11 +10986,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10729,11 +11008,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10751,11 +11030,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10773,11 +11052,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10795,11 +11074,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10817,11 +11096,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10839,11 +11118,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10861,11 +11140,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10883,11 +11162,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10905,11 +11184,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10927,11 +11206,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10949,11 +11228,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10971,11 +11250,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10993,11 +11272,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11015,11 +11294,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11037,11 +11316,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11059,11 +11338,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11081,11 +11360,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -11103,11 +11382,11 @@
       <c r="G402" s="14"/>
       <c r="H402" s="14"/>
       <c r="I402" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J402" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K402" s="16"/>
@@ -11125,11 +11404,11 @@
       <c r="G403" s="14"/>
       <c r="H403" s="14"/>
       <c r="I403" s="15" t="str">
-        <f t="shared" ref="I403:I414" si="16">IF(SUM(B403:F403,H403)=0,"",SUM(B403:F403,H403))</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J403" s="15" t="str">
-        <f t="shared" ref="J403:J414" si="17">IF(I403="","",1440-I403)</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K403" s="16"/>
@@ -11147,11 +11426,11 @@
       <c r="G404" s="14"/>
       <c r="H404" s="14"/>
       <c r="I404" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J404" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K404" s="16"/>
@@ -11169,11 +11448,11 @@
       <c r="G405" s="14"/>
       <c r="H405" s="14"/>
       <c r="I405" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J405" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K405" s="16"/>
@@ -11191,11 +11470,11 @@
       <c r="G406" s="14"/>
       <c r="H406" s="14"/>
       <c r="I406" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J406" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K406" s="16"/>
@@ -11213,11 +11492,11 @@
       <c r="G407" s="14"/>
       <c r="H407" s="14"/>
       <c r="I407" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J407" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K407" s="16"/>
@@ -11235,11 +11514,11 @@
       <c r="G408" s="14"/>
       <c r="H408" s="14"/>
       <c r="I408" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="I408:I419" si="20">IF(SUM(B408:F408,H408)=0,"",SUM(B408:F408,H408))</f>
         <v/>
       </c>
       <c r="J408" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="J408:J419" si="21">IF(I408="","",1440-I408)</f>
         <v/>
       </c>
       <c r="K408" s="16"/>
@@ -11257,11 +11536,11 @@
       <c r="G409" s="14"/>
       <c r="H409" s="14"/>
       <c r="I409" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J409" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K409" s="16"/>
@@ -11279,11 +11558,11 @@
       <c r="G410" s="14"/>
       <c r="H410" s="14"/>
       <c r="I410" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J410" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K410" s="16"/>
@@ -11301,11 +11580,11 @@
       <c r="G411" s="14"/>
       <c r="H411" s="14"/>
       <c r="I411" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J411" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K411" s="16"/>
@@ -11323,11 +11602,11 @@
       <c r="G412" s="14"/>
       <c r="H412" s="14"/>
       <c r="I412" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J412" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K412" s="16"/>
@@ -11345,11 +11624,11 @@
       <c r="G413" s="14"/>
       <c r="H413" s="14"/>
       <c r="I413" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J413" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K413" s="16"/>
@@ -11367,17 +11646,127 @@
       <c r="G414" s="14"/>
       <c r="H414" s="14"/>
       <c r="I414" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J414" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K414" s="16"/>
       <c r="L414" s="16"/>
       <c r="M414" s="16"/>
       <c r="N414" s="17"/>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A415" s="13"/>
+      <c r="B415" s="14"/>
+      <c r="C415" s="14"/>
+      <c r="D415" s="14"/>
+      <c r="E415" s="14"/>
+      <c r="F415" s="14"/>
+      <c r="G415" s="14"/>
+      <c r="H415" s="14"/>
+      <c r="I415" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J415" s="15" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K415" s="16"/>
+      <c r="L415" s="16"/>
+      <c r="M415" s="16"/>
+      <c r="N415" s="17"/>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A416" s="13"/>
+      <c r="B416" s="14"/>
+      <c r="C416" s="14"/>
+      <c r="D416" s="14"/>
+      <c r="E416" s="14"/>
+      <c r="F416" s="14"/>
+      <c r="G416" s="14"/>
+      <c r="H416" s="14"/>
+      <c r="I416" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J416" s="15" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K416" s="16"/>
+      <c r="L416" s="16"/>
+      <c r="M416" s="16"/>
+      <c r="N416" s="17"/>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A417" s="13"/>
+      <c r="B417" s="14"/>
+      <c r="C417" s="14"/>
+      <c r="D417" s="14"/>
+      <c r="E417" s="14"/>
+      <c r="F417" s="14"/>
+      <c r="G417" s="14"/>
+      <c r="H417" s="14"/>
+      <c r="I417" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J417" s="15" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K417" s="16"/>
+      <c r="L417" s="16"/>
+      <c r="M417" s="16"/>
+      <c r="N417" s="17"/>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A418" s="13"/>
+      <c r="B418" s="14"/>
+      <c r="C418" s="14"/>
+      <c r="D418" s="14"/>
+      <c r="E418" s="14"/>
+      <c r="F418" s="14"/>
+      <c r="G418" s="14"/>
+      <c r="H418" s="14"/>
+      <c r="I418" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J418" s="15" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K418" s="16"/>
+      <c r="L418" s="16"/>
+      <c r="M418" s="16"/>
+      <c r="N418" s="17"/>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A419" s="13"/>
+      <c r="B419" s="14"/>
+      <c r="C419" s="14"/>
+      <c r="D419" s="14"/>
+      <c r="E419" s="14"/>
+      <c r="F419" s="14"/>
+      <c r="G419" s="14"/>
+      <c r="H419" s="14"/>
+      <c r="I419" s="15" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="J419" s="15" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="K419" s="16"/>
+      <c r="L419" s="16"/>
+      <c r="M419" s="16"/>
+      <c r="N419" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11388,21 +11777,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J414">
+  <conditionalFormatting sqref="J6:J419">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K414" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K419" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L414" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L419" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M414" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M419" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="838" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9385B06-BA66-4CC9-A3B1-06FFF0F111E7}"/>
+  <xr:revisionPtr revIDLastSave="860" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C72F8B1-8056-4EC7-BDCE-32D16348B6AE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>met my all friends</t>
+  </si>
+  <si>
+    <t>enjoyed in gamezone</t>
   </si>
 </sst>
 </file>
@@ -4091,48 +4094,94 @@
       <c r="N70" s="17"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="14">
+        <v>400</v>
+      </c>
+      <c r="C71" s="14">
+        <v>0</v>
+      </c>
+      <c r="D71" s="14">
+        <v>60</v>
+      </c>
+      <c r="E71" s="14">
+        <v>60</v>
+      </c>
+      <c r="F71" s="14">
+        <v>350</v>
+      </c>
+      <c r="G71" s="14">
+        <v>7</v>
+      </c>
+      <c r="H71" s="14">
+        <v>290</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N71" s="17"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="14">
+        <v>360</v>
+      </c>
+      <c r="C72" s="14">
+        <v>0</v>
+      </c>
+      <c r="D72" s="14">
+        <v>100</v>
+      </c>
+      <c r="E72" s="14">
+        <v>50</v>
+      </c>
+      <c r="F72" s="14">
+        <v>200</v>
+      </c>
+      <c r="G72" s="14">
+        <v>4</v>
+      </c>
+      <c r="H72" s="14">
+        <v>360</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="860" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C72F8B1-8056-4EC7-BDCE-32D16348B6AE}"/>
+  <xr:revisionPtr revIDLastSave="888" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BADA3C5-8794-4E13-BAFC-74CEB0A0F83E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>enjoyed in gamezone</t>
+  </si>
+  <si>
+    <t>played pool</t>
   </si>
 </sst>
 </file>
@@ -4184,51 +4187,99 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="14">
+        <v>400</v>
+      </c>
+      <c r="C73" s="14">
+        <v>0</v>
+      </c>
+      <c r="D73" s="14">
+        <v>60</v>
+      </c>
+      <c r="E73" s="14">
+        <v>90</v>
+      </c>
+      <c r="F73" s="14">
+        <v>250</v>
+      </c>
+      <c r="G73" s="14">
+        <v>5</v>
+      </c>
+      <c r="H73" s="14">
+        <v>320</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="14">
+        <v>450</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>90</v>
+      </c>
+      <c r="E74" s="14">
+        <v>80</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>400</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="888" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BADA3C5-8794-4E13-BAFC-74CEB0A0F83E}"/>
+  <xr:revisionPtr revIDLastSave="922" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC782E0E-6E68-4B5D-9EDB-32734F8C192E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>played pool</t>
+  </si>
+  <si>
+    <t>a usual day</t>
+  </si>
+  <si>
+    <t>celebrated friends birthday</t>
   </si>
 </sst>
 </file>
@@ -4280,69 +4286,137 @@
       <c r="A75" s="8">
         <v>46320</v>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="B75" s="14">
+        <v>420</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>80</v>
+      </c>
+      <c r="E75" s="14">
+        <v>100</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>450</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="14">
+        <v>430</v>
+      </c>
+      <c r="C76" s="14">
+        <v>30</v>
+      </c>
+      <c r="D76" s="14">
+        <v>120</v>
+      </c>
+      <c r="E76" s="14">
+        <v>80</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="14">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14">
+        <v>400</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
+        <v>380</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="14">
+        <v>380</v>
+      </c>
+      <c r="C77" s="14">
+        <v>0</v>
+      </c>
+      <c r="D77" s="14">
+        <v>100</v>
+      </c>
+      <c r="E77" s="14">
+        <v>60</v>
+      </c>
+      <c r="F77" s="14">
+        <v>200</v>
+      </c>
+      <c r="G77" s="14">
+        <v>4</v>
+      </c>
+      <c r="H77" s="14">
+        <v>360</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>

--- a/12625080.xlsx
+++ b/12625080.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e149e35e993224e1/Desktop/Demo/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="922" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC782E0E-6E68-4B5D-9EDB-32734F8C192E}"/>
+  <xr:revisionPtr revIDLastSave="946" documentId="13_ncr:1_{C93A1E68-2BC2-4AA1-AA42-5607C2755F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86C0F176-EBA7-4AB7-B5B9-6227E006D73C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4419,47 +4419,91 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="14">
+        <v>400</v>
+      </c>
+      <c r="C78" s="14">
+        <v>0</v>
+      </c>
+      <c r="D78" s="14">
+        <v>80</v>
+      </c>
+      <c r="E78" s="14">
+        <v>80</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>320</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N78" s="17"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="14">
+        <v>380</v>
+      </c>
+      <c r="C79" s="14">
+        <v>0</v>
+      </c>
+      <c r="D79" s="14">
+        <v>60</v>
+      </c>
+      <c r="E79" s="14">
+        <v>120</v>
+      </c>
+      <c r="F79" s="14">
+        <v>200</v>
+      </c>
+      <c r="G79" s="14">
+        <v>4</v>
+      </c>
+      <c r="H79" s="14">
+        <v>395</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+        <v>285</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
